--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/MICHIGAN_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/MICHIGAN_2020.xlsx
@@ -3210,7 +3210,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C159">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C164">
@@ -3462,7 +3462,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C173">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C461">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C477">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>Ayotoxco De Guerero</t>
+          <t>Ayotoxco De Guerrero</t>
         </is>
       </c>
       <c r="C517">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>Ixcamilpa De Guerero</t>
+          <t>Ixcamilpa De Guerrero</t>
         </is>
       </c>
       <c r="C530">
@@ -10356,7 +10356,7 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C556">
